--- a/data/corpus/数据报表/职级薪酬表.xlsx
+++ b/data/corpus/数据报表/职级薪酬表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薪酬标准" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职级薪酬表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,31 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -57,33 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,206 +413,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>职级薪酬标准表</t>
-        </is>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>职级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>月薪下限</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>月薪上限</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>年终奖月数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>职级</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>基本工资</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>绩效工资</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>岗位津贴</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>年终奖系数</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>22000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>28000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>35000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E11" s="5" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>